--- a/fiis.xlsx
+++ b/fiis.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -5624,7 +5624,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -6524,7 +6524,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -7645,7 +7645,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -7915,7 +7915,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -8550,7 +8550,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -8860,7 +8860,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -9120,7 +9120,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -9175,7 +9175,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9230,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -9285,7 +9285,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -9555,7 +9555,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -9870,7 +9870,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -10035,7 +10035,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10090,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -10140,7 +10140,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -10240,7 +10240,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -10640,7 +10640,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -10690,7 +10690,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -10795,7 +10795,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -10900,7 +10900,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -11000,7 +11000,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -11310,7 +11310,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -11360,7 +11360,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -11460,7 +11460,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -11760,7 +11760,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -11865,7 +11865,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -11915,7 +11915,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -12025,7 +12025,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -12080,7 +12080,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -12142,7 +12142,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -12247,7 +12247,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -12302,7 +12302,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -12352,7 +12352,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -12452,7 +12452,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -12562,7 +12562,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -12622,7 +12622,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -12672,7 +12672,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -12722,7 +12722,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -12832,7 +12832,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -12982,7 +12982,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -13032,7 +13032,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -13292,7 +13292,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -13342,7 +13342,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -13397,7 +13397,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -13497,7 +13497,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -13547,7 +13547,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -13652,7 +13652,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -13702,7 +13702,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -13752,7 +13752,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -13802,7 +13802,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -13857,7 +13857,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -13912,7 +13912,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -13962,7 +13962,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -14072,7 +14072,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -14172,7 +14172,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -14222,7 +14222,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -14382,7 +14382,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -14432,7 +14432,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -14482,7 +14482,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -14592,7 +14592,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -14647,7 +14647,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -14702,7 +14702,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -14857,7 +14857,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -14907,7 +14907,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -14962,7 +14962,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -15112,7 +15112,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -15217,7 +15217,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -15272,7 +15272,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -15327,7 +15327,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -15382,7 +15382,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -15437,7 +15437,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -15602,7 +15602,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -15852,7 +15852,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -15907,7 +15907,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -15957,7 +15957,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -16012,7 +16012,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -16062,7 +16062,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -16117,7 +16117,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -16167,7 +16167,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -16267,7 +16267,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -16317,7 +16317,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -16372,7 +16372,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -16427,7 +16427,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -16532,7 +16532,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -16582,7 +16582,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -16637,7 +16637,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -16687,7 +16687,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -16744,7 +16744,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -16794,7 +16794,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -16899,7 +16899,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -16999,7 +16999,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -17054,7 +17054,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -17099,7 +17099,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -17204,7 +17204,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -17309,7 +17309,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -17359,7 +17359,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -17519,7 +17519,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -17569,7 +17569,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -17624,7 +17624,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -17724,7 +17724,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -17779,7 +17779,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -17829,7 +17829,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -17884,7 +17884,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -17989,7 +17989,7 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -18139,7 +18139,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -18239,7 +18239,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -18289,7 +18289,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -18344,7 +18344,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -18399,7 +18399,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -18504,7 +18504,7 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -18559,7 +18559,7 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -18724,7 +18724,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -18779,7 +18779,7 @@
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -18829,7 +18829,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -18884,7 +18884,7 @@
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -18939,7 +18939,7 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -18994,7 +18994,7 @@
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -19154,7 +19154,7 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -19204,7 +19204,7 @@
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -19249,7 +19249,7 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -19299,7 +19299,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -19349,7 +19349,7 @@
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -19404,7 +19404,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -19454,7 +19454,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="O365" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -19609,7 +19609,7 @@
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -19664,7 +19664,7 @@
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -19719,7 +19719,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -19829,7 +19829,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -20044,7 +20044,7 @@
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -20099,7 +20099,7 @@
       </c>
       <c r="O375" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="O376" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -20209,7 +20209,7 @@
       </c>
       <c r="O377" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -20264,7 +20264,7 @@
       </c>
       <c r="O378" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -20319,7 +20319,7 @@
       </c>
       <c r="O379" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -20374,7 +20374,7 @@
       </c>
       <c r="O380" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="O381" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -20484,7 +20484,7 @@
       </c>
       <c r="O382" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="O383" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="O384" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -20639,7 +20639,7 @@
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -20689,7 +20689,7 @@
       </c>
       <c r="O386" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -20739,7 +20739,7 @@
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -20794,7 +20794,7 @@
       </c>
       <c r="O388" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -20849,7 +20849,7 @@
       </c>
       <c r="O389" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -20899,7 +20899,7 @@
       </c>
       <c r="O390" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="O391" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="O392" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="O393" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -21099,7 +21099,7 @@
       </c>
       <c r="O394" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="O395" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="O396" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -21265,7 +21265,7 @@
       </c>
       <c r="O397" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -21320,7 +21320,7 @@
       </c>
       <c r="O398" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -21375,7 +21375,7 @@
       </c>
       <c r="O399" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -21425,7 +21425,7 @@
       </c>
       <c r="O400" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -21475,7 +21475,7 @@
       </c>
       <c r="O401" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -21525,7 +21525,7 @@
       </c>
       <c r="O402" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -21580,7 +21580,7 @@
       </c>
       <c r="O403" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -21630,7 +21630,7 @@
       </c>
       <c r="O404" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -21685,7 +21685,7 @@
       </c>
       <c r="O405" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -21735,7 +21735,7 @@
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -21790,7 +21790,7 @@
       </c>
       <c r="O407" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -21845,7 +21845,7 @@
       </c>
       <c r="O408" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -21895,7 +21895,7 @@
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="O410" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -22000,7 +22000,7 @@
       </c>
       <c r="O411" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -22050,7 +22050,7 @@
       </c>
       <c r="O412" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -22105,7 +22105,7 @@
       </c>
       <c r="O413" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -22155,7 +22155,7 @@
       </c>
       <c r="O414" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -22205,7 +22205,7 @@
       </c>
       <c r="O415" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="O416" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -22315,7 +22315,7 @@
       </c>
       <c r="O417" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -22373,7 +22373,7 @@
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -22428,7 +22428,7 @@
       </c>
       <c r="O419" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="O420" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -22538,7 +22538,7 @@
       </c>
       <c r="O421" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -22588,7 +22588,7 @@
       </c>
       <c r="O422" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -22643,7 +22643,7 @@
       </c>
       <c r="O423" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -22698,7 +22698,7 @@
       </c>
       <c r="O424" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -22753,7 +22753,7 @@
       </c>
       <c r="O425" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -22808,7 +22808,7 @@
       </c>
       <c r="O426" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
@@ -22858,7 +22858,7 @@
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-10-02</t>
         </is>
       </c>
     </row>
